--- a/artfynd/A 40425-2026 artfynd.xlsx
+++ b/artfynd/A 40425-2026 artfynd.xlsx
@@ -1785,7 +1785,7 @@
         <v>131673589</v>
       </c>
       <c r="B12" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>131673587</v>
       </c>
       <c r="B13" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 40425-2026 artfynd.xlsx
+++ b/artfynd/A 40425-2026 artfynd.xlsx
@@ -1814,11 +1814,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1926,11 +1922,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>

--- a/artfynd/A 40425-2026 artfynd.xlsx
+++ b/artfynd/A 40425-2026 artfynd.xlsx
@@ -1785,7 +1785,7 @@
         <v>131673589</v>
       </c>
       <c r="B12" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>131673587</v>
       </c>
       <c r="B13" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
